--- a/Team-Data/2011-12/4-13-2011-12.xlsx
+++ b/Team-Data/2011-12/4-13-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,55 +728,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.593</v>
+        <v>0.586</v>
       </c>
       <c r="H2" t="n">
         <v>49.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J2" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L2" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M2" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O2" t="n">
         <v>15.3</v>
       </c>
       <c r="P2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.738</v>
+        <v>0.736</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S2" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T2" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U2" t="n">
         <v>22.1</v>
@@ -724,22 +791,22 @@
         <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
@@ -754,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ2" t="n">
         <v>18</v>
@@ -763,28 +830,28 @@
         <v>14</v>
       </c>
       <c r="AL2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AM2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -796,13 +863,13 @@
         <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
         <v>6</v>
@@ -814,7 +881,7 @@
         <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
         <v>34</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.576</v>
+        <v>0.586</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L3" t="n">
         <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O3" t="n">
         <v>15.5</v>
@@ -888,7 +955,7 @@
         <v>7.8</v>
       </c>
       <c r="S3" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T3" t="n">
         <v>38.9</v>
@@ -897,10 +964,10 @@
         <v>23.8</v>
       </c>
       <c r="V3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X3" t="n">
         <v>5.5</v>
@@ -909,34 +976,34 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA3" t="n">
         <v>18.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>91.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -951,7 +1018,7 @@
         <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
         <v>23</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -975,7 +1042,7 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
         <v>19</v>
@@ -987,7 +1054,7 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>24</v>
@@ -996,7 +1063,7 @@
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>0.121</v>
+        <v>0.123</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
@@ -1043,67 +1110,67 @@
         <v>33.7</v>
       </c>
       <c r="J4" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.419</v>
+        <v>0.418</v>
       </c>
       <c r="L4" t="n">
         <v>4.1</v>
       </c>
       <c r="M4" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="N4" t="n">
         <v>0.304</v>
       </c>
       <c r="O4" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="R4" t="n">
         <v>10.2</v>
       </c>
       <c r="S4" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U4" t="n">
         <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W4" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="X4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y4" t="n">
         <v>5.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA4" t="n">
         <v>20.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>88</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.4</v>
+        <v>-13.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1121,7 +1188,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
@@ -1142,7 +1209,7 @@
         <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1154,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1172,7 +1239,7 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1315,7 +1382,7 @@
         <v>19</v>
       </c>
       <c r="AN5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
         <v>24</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1357,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="n">
         <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="J6" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="L6" t="n">
         <v>6.9</v>
@@ -1419,16 +1486,16 @@
         <v>19.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.714</v>
+        <v>0.711</v>
       </c>
       <c r="R6" t="n">
         <v>13</v>
@@ -1440,10 +1507,10 @@
         <v>42.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V6" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1455,19 +1522,19 @@
         <v>6.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
         <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1476,7 +1543,7 @@
         <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH6" t="n">
         <v>7</v>
@@ -1485,7 +1552,7 @@
         <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
@@ -1494,7 +1561,7 @@
         <v>13</v>
       </c>
       <c r="AM6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN6" t="n">
         <v>12</v>
@@ -1515,13 +1582,13 @@
         <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW6" t="n">
         <v>22</v>
@@ -1539,10 +1606,10 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
         <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J7" t="n">
         <v>81.8</v>
@@ -1595,52 +1662,52 @@
         <v>0.442</v>
       </c>
       <c r="L7" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M7" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0.336</v>
+        <v>0.334</v>
       </c>
       <c r="O7" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="P7" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R7" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S7" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U7" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V7" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
         <v>8.6</v>
       </c>
       <c r="X7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AB7" t="n">
         <v>95</v>
@@ -1649,10 +1716,10 @@
         <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1661,10 +1728,10 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ7" t="n">
         <v>14</v>
@@ -1679,31 +1746,31 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>28</v>
       </c>
       <c r="AP7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1724,7 +1791,7 @@
         <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -1753,64 +1820,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
         <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.542</v>
+        <v>0.552</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
       </c>
       <c r="I8" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J8" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="L8" t="n">
         <v>6.7</v>
       </c>
       <c r="M8" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.328</v>
+        <v>0.329</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="P8" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R8" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T8" t="n">
         <v>43.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
         <v>15.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="X8" t="n">
         <v>5.1</v>
@@ -1822,22 +1889,22 @@
         <v>19.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.6</v>
+        <v>103.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>13</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -1849,10 +1916,10 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
         <v>16</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
@@ -1879,19 +1946,19 @@
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
         <v>27</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>30</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.373</v>
+        <v>0.379</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1956,7 +2023,7 @@
         <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
@@ -1965,67 +2032,67 @@
         <v>13.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
         <v>22.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S9" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U9" t="n">
         <v>18.6</v>
       </c>
       <c r="V9" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W9" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
         <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z9" t="n">
         <v>19.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>25</v>
@@ -2034,7 +2101,7 @@
         <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2052,7 +2119,7 @@
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
@@ -2079,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
         <v>16</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2216,7 +2283,7 @@
         <v>11</v>
       </c>
       <c r="AK10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2252,7 +2319,7 @@
         <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" t="n">
         <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.542</v>
+        <v>0.552</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
@@ -2329,16 +2396,16 @@
         <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.36</v>
+        <v>0.362</v>
       </c>
       <c r="O11" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.791</v>
+        <v>0.789</v>
       </c>
       <c r="R11" t="n">
         <v>11.6</v>
@@ -2347,10 +2414,10 @@
         <v>30.5</v>
       </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U11" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V11" t="n">
         <v>14.5</v>
@@ -2362,28 +2429,28 @@
         <v>4.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -2395,10 +2462,10 @@
         <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL11" t="n">
         <v>12</v>
@@ -2407,13 +2474,13 @@
         <v>17</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
@@ -2437,7 +2504,7 @@
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY11" t="n">
         <v>20</v>
@@ -2449,7 +2516,7 @@
         <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J12" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.44</v>
@@ -2508,10 +2575,10 @@
         <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O12" t="n">
         <v>20.4</v>
@@ -2520,7 +2587,7 @@
         <v>26.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R12" t="n">
         <v>12.1</v>
@@ -2529,10 +2596,10 @@
         <v>31.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="V12" t="n">
         <v>14.4</v>
@@ -2550,16 +2617,16 @@
         <v>21.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2574,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ12" t="n">
         <v>22</v>
@@ -2595,16 +2662,16 @@
         <v>2</v>
       </c>
       <c r="AP12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -2634,7 +2701,7 @@
         <v>15</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>7</v>
@@ -2753,7 +2820,7 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI13" t="n">
         <v>13</v>
@@ -2774,7 +2841,7 @@
         <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
         <v>25</v>
@@ -2792,7 +2859,7 @@
         <v>18</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV13" t="n">
         <v>2</v>
@@ -2804,10 +2871,10 @@
         <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
@@ -2816,7 +2883,7 @@
         <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.633</v>
+        <v>0.627</v>
       </c>
       <c r="H14" t="n">
         <v>48.5</v>
@@ -2863,10 +2930,10 @@
         <v>36.6</v>
       </c>
       <c r="J14" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K14" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L14" t="n">
         <v>5.5</v>
@@ -2875,19 +2942,19 @@
         <v>17.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.324</v>
+        <v>0.321</v>
       </c>
       <c r="O14" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R14" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S14" t="n">
         <v>34.2</v>
@@ -2896,34 +2963,34 @@
         <v>46.2</v>
       </c>
       <c r="U14" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V14" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X14" t="n">
         <v>5.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="AA14" t="n">
         <v>20.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2953,7 +3020,7 @@
         <v>18</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO14" t="n">
         <v>8</v>
@@ -2962,7 +3029,7 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>11</v>
@@ -2977,7 +3044,7 @@
         <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
@@ -2992,13 +3059,13 @@
         <v>1</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF15" t="n">
         <v>8</v>
       </c>
       <c r="AG15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH15" t="n">
         <v>14</v>
@@ -3144,10 +3211,10 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
         <v>22</v>
@@ -3165,22 +3232,22 @@
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.707</v>
+        <v>0.702</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J16" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M16" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.366</v>
+        <v>0.369</v>
       </c>
       <c r="O16" t="n">
         <v>19.3</v>
       </c>
       <c r="P16" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R16" t="n">
         <v>10.4</v>
@@ -3260,10 +3327,10 @@
         <v>41.6</v>
       </c>
       <c r="U16" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V16" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W16" t="n">
         <v>9.1</v>
@@ -3281,16 +3348,16 @@
         <v>20.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
@@ -3302,7 +3369,7 @@
         <v>3</v>
       </c>
       <c r="AI16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -3311,13 +3378,13 @@
         <v>2</v>
       </c>
       <c r="AL16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="n">
         <v>23</v>
       </c>
       <c r="AN16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO16" t="n">
         <v>5</v>
@@ -3326,22 +3393,22 @@
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW16" t="n">
         <v>3</v>
@@ -3353,7 +3420,7 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>7</v>
@@ -3362,7 +3429,7 @@
         <v>4</v>
       </c>
       <c r="BC16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -3391,31 +3458,31 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="n">
         <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>0.492</v>
+        <v>0.483</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J17" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L17" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M17" t="n">
         <v>19.5</v>
@@ -3430,7 +3497,7 @@
         <v>20.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R17" t="n">
         <v>12.5</v>
@@ -3442,7 +3509,7 @@
         <v>41.9</v>
       </c>
       <c r="U17" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="n">
         <v>14.1</v>
@@ -3451,7 +3518,7 @@
         <v>8.4</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
         <v>4.6</v>
@@ -3463,13 +3530,13 @@
         <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3484,25 +3551,25 @@
         <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
       </c>
       <c r="AK17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO17" t="n">
         <v>17</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>18</v>
       </c>
       <c r="AP17" t="n">
         <v>24</v>
@@ -3511,7 +3578,7 @@
         <v>6</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
         <v>26</v>
@@ -3520,19 +3587,19 @@
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
         <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
@@ -3541,10 +3608,10 @@
         <v>19</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -3675,22 +3742,22 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
         <v>4</v>
       </c>
       <c r="AP18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
@@ -3705,7 +3772,7 @@
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
@@ -3717,13 +3784,13 @@
         <v>23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
         <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.367</v>
+        <v>0.356</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3782,28 +3849,28 @@
         <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="N19" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O19" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P19" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0.775</v>
       </c>
       <c r="R19" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="T19" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U19" t="n">
         <v>20.1</v>
@@ -3827,19 +3894,19 @@
         <v>19.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.2</v>
+        <v>-5.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG19" t="n">
         <v>24</v>
@@ -3851,7 +3918,7 @@
         <v>28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3863,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3875,7 +3942,7 @@
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3887,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
         <v>16</v>
@@ -3899,16 +3966,16 @@
         <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA19" t="n">
         <v>15</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
         <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.288</v>
+        <v>0.276</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,19 +4022,19 @@
         <v>35.2</v>
       </c>
       <c r="J20" t="n">
-        <v>77.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O20" t="n">
         <v>15.3</v>
@@ -3976,19 +4043,19 @@
         <v>20.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R20" t="n">
         <v>11.1</v>
       </c>
       <c r="S20" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U20" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V20" t="n">
         <v>15.4</v>
@@ -4006,16 +4073,16 @@
         <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>89.8</v>
+        <v>89.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>29</v>
@@ -4045,22 +4112,22 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP20" t="n">
         <v>25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS20" t="n">
         <v>19</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4069,19 +4136,19 @@
         <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW20" t="n">
         <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -4119,61 +4186,61 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
         <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
         <v>81</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L21" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M21" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.323</v>
+        <v>0.32</v>
       </c>
       <c r="O21" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P21" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R21" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S21" t="n">
         <v>30.8</v>
       </c>
       <c r="T21" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U21" t="n">
         <v>19.7</v>
       </c>
       <c r="V21" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W21" t="n">
         <v>9.5</v>
@@ -4182,34 +4249,34 @@
         <v>4.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4227,7 +4294,7 @@
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
@@ -4263,16 +4330,16 @@
         <v>18</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA21" t="n">
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F22" t="n">
         <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.729</v>
+        <v>0.724</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J22" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K22" t="n">
         <v>0.474</v>
@@ -4328,7 +4395,7 @@
         <v>7.2</v>
       </c>
       <c r="M22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
         <v>0.36</v>
@@ -4337,19 +4404,19 @@
         <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="R22" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T22" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U22" t="n">
         <v>18.5</v>
@@ -4358,7 +4425,7 @@
         <v>16.4</v>
       </c>
       <c r="W22" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X22" t="n">
         <v>8.1</v>
@@ -4367,19 +4434,19 @@
         <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.9</v>
+        <v>102.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4403,19 +4470,19 @@
         <v>1</v>
       </c>
       <c r="AL22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
@@ -4424,10 +4491,10 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>29</v>
@@ -4445,7 +4512,7 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
         <v>14</v>
@@ -4454,7 +4521,7 @@
         <v>2</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
         <v>34</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
-        <v>0.576</v>
+        <v>0.586</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4501,10 +4568,10 @@
         <v>34.3</v>
       </c>
       <c r="J23" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L23" t="n">
         <v>10.2</v>
@@ -4513,13 +4580,13 @@
         <v>26.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.378</v>
+        <v>0.381</v>
       </c>
       <c r="O23" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P23" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q23" t="n">
         <v>0.654</v>
@@ -4531,10 +4598,10 @@
         <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
         <v>15.2</v>
@@ -4543,37 +4610,37 @@
         <v>6.7</v>
       </c>
       <c r="X23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
         <v>4.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>94</v>
+        <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
         <v>29</v>
@@ -4591,10 +4658,10 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -4603,19 +4670,19 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
         <v>26</v>
@@ -4630,13 +4697,13 @@
         <v>4</v>
       </c>
       <c r="BA23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
         <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>0.525</v>
+        <v>0.534</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J24" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L24" t="n">
         <v>5.2</v>
@@ -4695,13 +4762,13 @@
         <v>14.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.358</v>
+        <v>0.361</v>
       </c>
       <c r="O24" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="P24" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0.741</v>
@@ -4710,16 +4777,16 @@
         <v>10.4</v>
       </c>
       <c r="S24" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T24" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U24" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V24" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="W24" t="n">
         <v>8.1</v>
@@ -4728,22 +4795,22 @@
         <v>5.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
         <v>17.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="AB24" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4758,7 +4825,7 @@
         <v>26</v>
       </c>
       <c r="AI24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
         <v>5</v>
@@ -4773,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,16 +4861,16 @@
         <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
         <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
@@ -4865,37 +4932,37 @@
         <v>37.6</v>
       </c>
       <c r="J25" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K25" t="n">
         <v>0.458</v>
       </c>
       <c r="L25" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O25" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="P25" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R25" t="n">
         <v>10.7</v>
       </c>
       <c r="S25" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
         <v>22.7</v>
@@ -4904,7 +4971,7 @@
         <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X25" t="n">
         <v>5.6</v>
@@ -4913,64 +4980,64 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>98.09999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM25" t="n">
         <v>13</v>
       </c>
-      <c r="AK25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>14</v>
-      </c>
       <c r="AN25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>21</v>
@@ -4991,16 +5058,16 @@
         <v>3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" t="n">
-        <v>0.467</v>
+        <v>0.475</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5059,13 +5126,13 @@
         <v>20.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O26" t="n">
         <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0.797</v>
@@ -5077,7 +5144,7 @@
         <v>29.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U26" t="n">
         <v>20.6</v>
@@ -5107,10 +5174,10 @@
         <v>0.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
         <v>20</v>
@@ -5119,40 +5186,40 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL26" t="n">
         <v>10</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>11</v>
       </c>
       <c r="AM26" t="n">
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
         <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5164,25 +5231,25 @@
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX26" t="n">
         <v>16</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA26" t="n">
         <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -5211,52 +5278,52 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>0.317</v>
+        <v>0.322</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J27" t="n">
-        <v>86.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
       <c r="L27" t="n">
         <v>6.3</v>
       </c>
       <c r="M27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>0.315</v>
+        <v>0.314</v>
       </c>
       <c r="O27" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q27" t="n">
         <v>0.738</v>
       </c>
       <c r="R27" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="S27" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T27" t="n">
         <v>43.3</v>
@@ -5274,22 +5341,22 @@
         <v>4.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.3</v>
+        <v>-5.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5301,7 +5368,7 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
@@ -5316,7 +5383,7 @@
         <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN27" t="n">
         <v>28</v>
@@ -5328,43 +5395,43 @@
         <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
         <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>5.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,10 +5556,10 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL28" t="n">
         <v>2</v>
@@ -5504,13 +5571,13 @@
         <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
         <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J29" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L29" t="n">
         <v>5.6</v>
@@ -5605,34 +5672,34 @@
         <v>16.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O29" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P29" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
       </c>
       <c r="S29" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T29" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
         <v>15</v>
       </c>
       <c r="W29" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X29" t="n">
         <v>4.9</v>
@@ -5641,19 +5708,19 @@
         <v>5</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
@@ -5662,10 +5729,10 @@
         <v>26</v>
       </c>
       <c r="AG29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI29" t="n">
         <v>27</v>
@@ -5677,7 +5744,7 @@
         <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="n">
         <v>20</v>
@@ -5689,7 +5756,7 @@
         <v>15</v>
       </c>
       <c r="AP29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ29" t="n">
         <v>11</v>
@@ -5698,31 +5765,31 @@
         <v>22</v>
       </c>
       <c r="AS29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>19</v>
       </c>
       <c r="AU29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW29" t="n">
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.517</v>
+        <v>0.525</v>
       </c>
       <c r="H30" t="n">
         <v>48.8</v>
       </c>
       <c r="I30" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J30" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.456</v>
@@ -5787,7 +5854,7 @@
         <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.31</v>
+        <v>0.312</v>
       </c>
       <c r="O30" t="n">
         <v>18.8</v>
@@ -5796,13 +5863,13 @@
         <v>25.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="R30" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S30" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
         <v>43.8</v>
@@ -5826,34 +5893,34 @@
         <v>22</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
       </c>
       <c r="AF30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
       </c>
       <c r="AI30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK30" t="n">
         <v>9</v>
@@ -5871,28 +5938,28 @@
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT30" t="n">
         <v>4</v>
       </c>
       <c r="AU30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV30" t="n">
         <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX30" t="n">
         <v>4</v>
@@ -5907,10 +5974,10 @@
         <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>0.237</v>
+        <v>0.241</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="L31" t="n">
         <v>5.3</v>
       </c>
       <c r="M31" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.321</v>
+        <v>0.324</v>
       </c>
       <c r="O31" t="n">
         <v>15.7</v>
@@ -5978,46 +6045,46 @@
         <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
         <v>29.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U31" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="V31" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W31" t="n">
         <v>7.7</v>
       </c>
       <c r="X31" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y31" t="n">
         <v>4.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.7</v>
+        <v>-6.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6032,13 +6099,13 @@
         <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
         <v>24</v>
@@ -6047,10 +6114,10 @@
         <v>21</v>
       </c>
       <c r="AN31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
@@ -6062,16 +6129,16 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>15</v>
@@ -6086,7 +6153,7 @@
         <v>26</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-13-2011-12</t>
+          <t>2012-04-13</t>
         </is>
       </c>
     </row>
